--- a/DOKU-STUFF/DOKU/RACK_Belegung.xlsx
+++ b/DOKU-STUFF/DOKU/RACK_Belegung.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\GRAF_MNP\DOKU-STUFF\DOKU\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7764A412-1A63-47A8-8AF0-25EAE792BDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -62,8 +63,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +76,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -115,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -123,6 +131,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -404,7 +416,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -445,13 +457,13 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="6">
         <v>64</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="6">
         <v>3</v>
       </c>
     </row>
@@ -501,6 +513,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>